--- a/AAII_Financials/Quarterly/LXEH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LXEH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="92">
   <si>
     <t>LXEH</t>
   </si>
@@ -1122,11 +1122,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1444,10 +1444,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5900</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>5800</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
@@ -1512,10 +1512,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-7200</v>
+        <v>-1200</v>
       </c>
       <c r="E21" s="3">
-        <v>-7100</v>
+        <v>-1200</v>
       </c>
       <c r="F21" s="3">
         <v>-800</v>
@@ -2260,10 +2260,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5900</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>-5800</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
@@ -2793,10 +2793,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="E43" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="F43" s="3">
         <v>1500</v>
@@ -2929,10 +2929,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="E45" s="3">
-        <v>1700</v>
+        <v>600</v>
       </c>
       <c r="F45" s="3">
         <v>500</v>
@@ -3729,10 +3729,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13500</v>
+        <v>14500</v>
       </c>
       <c r="E58" s="3">
-        <v>13300</v>
+        <v>14300</v>
       </c>
       <c r="F58" s="3">
         <v>13100</v>
@@ -3797,10 +3797,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1400</v>
+        <v>1900</v>
       </c>
       <c r="E59" s="3">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="F59" s="3">
         <v>1700</v>
